--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_arica_y_parinacota_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:22</t>
+    <t xml:space="preserve">2026-09-29 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_arica_y_parinacota_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:13</t>
+    <t xml:space="preserve">2026-09-29 18:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>30.62</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>35.35</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         <v>-25.12</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>110.29</v>
+        <v>110.3</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>135.42</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_arica_y_parinacota_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:48</t>
+    <t xml:space="preserve">2026-10-05 04:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,10 +487,10 @@
         <v>-4.72</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>30.62</v>
+        <v>30.63</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>35.34</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="3">
